--- a/api/1/xlsx/en/SectorGroup.xlsx
+++ b/api/1/xlsx/en/SectorGroup.xlsx
@@ -25,18 +25,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-name</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
-    <t>codeforiati:category-name</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,18 +46,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>Education, Level Unspecified</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>Education, Level Unspecified</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>Primary education</t>
   </si>
   <si>
+    <t>Basic Education</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
-    <t>Basic Education</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>Upper Secondary Education (modified and includes data from 11322)</t>
   </si>
   <si>
+    <t>Secondary Education</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
-    <t>Secondary Education</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -148,12 +148,12 @@
     <t>Higher education</t>
   </si>
   <si>
+    <t>Post-Secondary Education</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
-    <t>Post-Secondary Education</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -166,18 +166,18 @@
     <t>Health policy and administrative management</t>
   </si>
   <si>
+    <t>Health, General</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>Health</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
-    <t>Health</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>Health, General</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -202,12 +202,12 @@
     <t>Basic health care</t>
   </si>
   <si>
+    <t>Basic Health</t>
+  </si>
+  <si>
     <t>122</t>
   </si>
   <si>
-    <t>Basic Health</t>
-  </si>
-  <si>
     <t>12230</t>
   </si>
   <si>
@@ -262,12 +262,12 @@
     <t>NCDs control, general</t>
   </si>
   <si>
+    <t>Non-communicable diseases (NCDs)</t>
+  </si>
+  <si>
     <t>123</t>
   </si>
   <si>
-    <t>Non-communicable diseases (NCDs)</t>
-  </si>
-  <si>
     <t>12320</t>
   </si>
   <si>
@@ -304,12 +304,12 @@
     <t>Population policy and administrative management</t>
   </si>
   <si>
+    <t>Population Policies/Programmes &amp; Reproductive Health</t>
+  </si>
+  <si>
     <t>130</t>
   </si>
   <si>
-    <t>Population Policies/Programmes &amp; Reproductive Health</t>
-  </si>
-  <si>
     <t>13020</t>
   </si>
   <si>
@@ -340,12 +340,12 @@
     <t>Water sector policy and administrative management</t>
   </si>
   <si>
+    <t>Water Supply &amp; Sanitation</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
-    <t>Water Supply &amp; Sanitation</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -412,18 +412,18 @@
     <t>Public sector policy and administrative management</t>
   </si>
   <si>
+    <t>Government &amp; Civil Society-general</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Government &amp; Civil Society</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>Government &amp; Civil Society</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>Government &amp; Civil Society-general</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -520,12 +520,12 @@
     <t>Security system management and reform</t>
   </si>
   <si>
+    <t>Conflict, Peace &amp; Security</t>
+  </si>
+  <si>
     <t>152</t>
   </si>
   <si>
-    <t>Conflict, Peace &amp; Security</t>
-  </si>
-  <si>
     <t>15220</t>
   </si>
   <si>
@@ -562,12 +562,12 @@
     <t>Social Protection</t>
   </si>
   <si>
+    <t>Other Social Infrastructure &amp; Services</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
-    <t>Other Social Infrastructure &amp; Services</t>
-  </si>
-  <si>
     <t>16020</t>
   </si>
   <si>
@@ -634,12 +634,12 @@
     <t>Transport policy and administrative management</t>
   </si>
   <si>
+    <t>Transport &amp; Storage</t>
+  </si>
+  <si>
     <t>210</t>
   </si>
   <si>
-    <t>Transport &amp; Storage</t>
-  </si>
-  <si>
     <t>21020</t>
   </si>
   <si>
@@ -682,12 +682,12 @@
     <t>Communications policy and administrative management</t>
   </si>
   <si>
+    <t>Communications</t>
+  </si>
+  <si>
     <t>220</t>
   </si>
   <si>
-    <t>Communications</t>
-  </si>
-  <si>
     <t>22020</t>
   </si>
   <si>
@@ -712,18 +712,18 @@
     <t>Energy policy and administrative management</t>
   </si>
   <si>
+    <t>Energy Policy</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
-    <t>Energy</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>Energy Policy</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -748,12 +748,12 @@
     <t>Energy generation, renewable sources - multiple technologies</t>
   </si>
   <si>
+    <t>Energy generation, renewable sources</t>
+  </si>
+  <si>
     <t>232</t>
   </si>
   <si>
-    <t>Energy generation, renewable sources</t>
-  </si>
-  <si>
     <t>23220</t>
   </si>
   <si>
@@ -808,12 +808,12 @@
     <t>Energy generation, non-renewable sources, unspecified</t>
   </si>
   <si>
+    <t>Energy generation, non-renewable sources</t>
+  </si>
+  <si>
     <t>233</t>
   </si>
   <si>
-    <t>Energy generation, non-renewable sources</t>
-  </si>
-  <si>
     <t>23320</t>
   </si>
   <si>
@@ -850,36 +850,36 @@
     <t>Hybrid energy electric power plants</t>
   </si>
   <si>
+    <t>Hybrid energy plants</t>
+  </si>
+  <si>
     <t>234</t>
   </si>
   <si>
-    <t>Hybrid energy plants</t>
-  </si>
-  <si>
     <t>23510</t>
   </si>
   <si>
     <t>Nuclear energy electric power plants and nuclear safety</t>
   </si>
   <si>
+    <t>Nuclear energy plants</t>
+  </si>
+  <si>
     <t>235</t>
   </si>
   <si>
-    <t>Nuclear energy plants</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
     <t>Heat plants</t>
   </si>
   <si>
+    <t>Energy distribution</t>
+  </si>
+  <si>
     <t>236</t>
   </si>
   <si>
-    <t>Energy distribution</t>
-  </si>
-  <si>
     <t>23620</t>
   </si>
   <si>
@@ -922,12 +922,12 @@
     <t>Financial policy and administrative management</t>
   </si>
   <si>
+    <t>Banking &amp; Financial Services</t>
+  </si>
+  <si>
     <t>240</t>
   </si>
   <si>
-    <t>Banking &amp; Financial Services</t>
-  </si>
-  <si>
     <t>24020</t>
   </si>
   <si>
@@ -964,12 +964,12 @@
     <t>Business policy and administration</t>
   </si>
   <si>
+    <t>Business &amp; Other Services</t>
+  </si>
+  <si>
     <t>250</t>
   </si>
   <si>
-    <t>Business &amp; Other Services</t>
-  </si>
-  <si>
     <t>25020</t>
   </si>
   <si>
@@ -994,18 +994,18 @@
     <t>Agricultural policy and administrative management</t>
   </si>
   <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Agriculture, Forestry, Fishing</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
-    <t>Agriculture, Forestry, Fishing</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1114,12 +1114,12 @@
     <t>Forestry policy and administrative management</t>
   </si>
   <si>
+    <t>Forestry</t>
+  </si>
+  <si>
     <t>312</t>
   </si>
   <si>
-    <t>Forestry</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1156,12 +1156,12 @@
     <t>Fishing policy and administrative management</t>
   </si>
   <si>
+    <t>Fishing</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
-    <t>Fishing</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1192,18 +1192,18 @@
     <t>Industrial policy and administrative management</t>
   </si>
   <si>
+    <t>Industry</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>Industry, Mining, Construction</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
-    <t>Industry, Mining, Construction</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>Industry</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1318,12 +1318,12 @@
     <t>Mineral/mining policy and administrative management</t>
   </si>
   <si>
+    <t>Mineral Resources &amp; Mining</t>
+  </si>
+  <si>
     <t>322</t>
   </si>
   <si>
-    <t>Mineral Resources &amp; Mining</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1384,24 +1384,24 @@
     <t>Construction policy and administrative management</t>
   </si>
   <si>
+    <t>Construction</t>
+  </si>
+  <si>
     <t>323</t>
   </si>
   <si>
-    <t>Construction</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
     <t>Trade policy and administrative management</t>
   </si>
   <si>
+    <t>Trade Policies &amp; Regulations</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>Trade Policies &amp; Regulations</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1438,24 +1438,24 @@
     <t>Tourism policy and administrative management</t>
   </si>
   <si>
+    <t>Tourism</t>
+  </si>
+  <si>
     <t>332</t>
   </si>
   <si>
-    <t>Tourism</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
     <t>Environmental policy and administrative management</t>
   </si>
   <si>
+    <t>General Environment Protection</t>
+  </si>
+  <si>
     <t>410</t>
   </si>
   <si>
-    <t>General Environment Protection</t>
-  </si>
-  <si>
     <t>41020</t>
   </si>
   <si>
@@ -1492,12 +1492,12 @@
     <t>Multisector aid</t>
   </si>
   <si>
+    <t>Other Multisector</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
-    <t>Other Multisector</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1558,36 +1558,36 @@
     <t>General budget support-related aid</t>
   </si>
   <si>
+    <t>General Budget Support</t>
+  </si>
+  <si>
     <t>510</t>
   </si>
   <si>
-    <t>General Budget Support</t>
-  </si>
-  <si>
     <t>52010</t>
   </si>
   <si>
     <t>Food assistance</t>
   </si>
   <si>
+    <t>Development Food Assistance</t>
+  </si>
+  <si>
     <t>520</t>
   </si>
   <si>
-    <t>Development Food Assistance</t>
-  </si>
-  <si>
     <t>53030</t>
   </si>
   <si>
     <t>Import support (capital goods)</t>
   </si>
   <si>
+    <t>Other Commodity Assistance</t>
+  </si>
+  <si>
     <t>530</t>
   </si>
   <si>
-    <t>Other Commodity Assistance</t>
-  </si>
-  <si>
     <t>53040</t>
   </si>
   <si>
@@ -1600,12 +1600,12 @@
     <t>Action relating to debt</t>
   </si>
   <si>
+    <t>Action Relating to Debt</t>
+  </si>
+  <si>
     <t>600</t>
   </si>
   <si>
-    <t>Action Relating to Debt</t>
-  </si>
-  <si>
     <t>60020</t>
   </si>
   <si>
@@ -1648,12 +1648,12 @@
     <t>Material relief assistance and services</t>
   </si>
   <si>
+    <t>Emergency Response</t>
+  </si>
+  <si>
     <t>720</t>
   </si>
   <si>
-    <t>Emergency Response</t>
-  </si>
-  <si>
     <t>72040</t>
   </si>
   <si>
@@ -1672,58 +1672,58 @@
     <t>Immediate post-emergency reconstruction and rehabilitation</t>
   </si>
   <si>
+    <t>Reconstruction Relief &amp; Rehabilitation</t>
+  </si>
+  <si>
     <t>730</t>
   </si>
   <si>
-    <t>Reconstruction Relief &amp; Rehabilitation</t>
-  </si>
-  <si>
     <t>74020</t>
   </si>
   <si>
     <t>Multi-hazard response preparedness</t>
   </si>
   <si>
+    <t>Disaster Prevention &amp; Preparedness</t>
+  </si>
+  <si>
     <t>740</t>
   </si>
   <si>
-    <t>Disaster Prevention &amp; Preparedness</t>
-  </si>
-  <si>
     <t>91010</t>
   </si>
   <si>
     <t>Administrative costs (non-sector allocable)</t>
   </si>
   <si>
+    <t>Administrative Costs of Donors</t>
+  </si>
+  <si>
     <t>910</t>
   </si>
   <si>
-    <t>Administrative Costs of Donors</t>
-  </si>
-  <si>
     <t>93010</t>
   </si>
   <si>
     <t>Refugees/asylum seekers in donor countries (non-sector allocable)</t>
   </si>
   <si>
+    <t>Refugees in Donor Countries</t>
+  </si>
+  <si>
     <t>930</t>
   </si>
   <si>
-    <t>Refugees in Donor Countries</t>
-  </si>
-  <si>
     <t>99810</t>
   </si>
   <si>
     <t>Sectors not specified</t>
   </si>
   <si>
+    <t>Unallocated / Unspecified</t>
+  </si>
+  <si>
     <t>998</t>
-  </si>
-  <si>
-    <t>Unallocated / Unspecified</t>
   </si>
   <si>
     <t>99820</t>

--- a/api/1/xlsx/en/SectorGroup.xlsx
+++ b/api/1/xlsx/en/SectorGroup.xlsx
@@ -28,15 +28,15 @@
     <t>codeforiati:category-name</t>
   </si>
   <si>
+    <t>codeforiati:group-name</t>
+  </si>
+  <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:group-name</t>
-  </si>
-  <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -49,15 +49,15 @@
     <t>Education, Level Unspecified</t>
   </si>
   <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -169,15 +169,15 @@
     <t>Health, General</t>
   </si>
   <si>
+    <t>Health</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>Health</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -415,15 +415,15 @@
     <t>Government &amp; Civil Society-general</t>
   </si>
   <si>
+    <t>Government &amp; Civil Society</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>Government &amp; Civil Society</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -715,15 +715,15 @@
     <t>Energy Policy</t>
   </si>
   <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>Energy</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -997,15 +997,15 @@
     <t>Agriculture</t>
   </si>
   <si>
+    <t>Agriculture, Forestry, Fishing</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>Agriculture, Forestry, Fishing</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1195,13 +1195,13 @@
     <t>Industry</t>
   </si>
   <si>
+    <t>Industry, Mining, Construction</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
     <t>320</t>
-  </si>
-  <si>
-    <t>Industry, Mining, Construction</t>
-  </si>
-  <si>
-    <t>321</t>
   </si>
   <si>
     <t>32120</t>
@@ -2196,10 +2196,10 @@
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2219,10 +2219,10 @@
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2242,10 +2242,10 @@
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2265,10 +2265,10 @@
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2288,10 +2288,10 @@
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G10" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2311,10 +2311,10 @@
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G11" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2334,10 +2334,10 @@
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G12" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2357,10 +2357,10 @@
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2380,10 +2380,10 @@
         <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G14" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2403,10 +2403,10 @@
         <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="G15" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2426,10 +2426,10 @@
         <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="G16" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2541,10 +2541,10 @@
         <v>51</v>
       </c>
       <c r="F21" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G21" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2564,10 +2564,10 @@
         <v>51</v>
       </c>
       <c r="F22" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G22" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2587,10 +2587,10 @@
         <v>51</v>
       </c>
       <c r="F23" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G23" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2610,10 +2610,10 @@
         <v>51</v>
       </c>
       <c r="F24" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G24" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2633,10 +2633,10 @@
         <v>51</v>
       </c>
       <c r="F25" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G25" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2656,10 +2656,10 @@
         <v>51</v>
       </c>
       <c r="F26" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G26" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2679,10 +2679,10 @@
         <v>51</v>
       </c>
       <c r="F27" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G27" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2702,10 +2702,10 @@
         <v>51</v>
       </c>
       <c r="F28" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G28" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2725,10 +2725,10 @@
         <v>51</v>
       </c>
       <c r="F29" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G29" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2748,10 +2748,10 @@
         <v>51</v>
       </c>
       <c r="F30" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="G30" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2771,10 +2771,10 @@
         <v>51</v>
       </c>
       <c r="F31" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="G31" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2794,10 +2794,10 @@
         <v>51</v>
       </c>
       <c r="F32" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="G32" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2817,10 +2817,10 @@
         <v>51</v>
       </c>
       <c r="F33" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="G33" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2840,10 +2840,10 @@
         <v>51</v>
       </c>
       <c r="F34" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="G34" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2863,10 +2863,10 @@
         <v>51</v>
       </c>
       <c r="F35" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="G35" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2883,10 +2883,10 @@
         <v>96</v>
       </c>
       <c r="E36" t="s">
+        <v>96</v>
+      </c>
+      <c r="F36" t="s">
         <v>97</v>
-      </c>
-      <c r="F36" t="s">
-        <v>96</v>
       </c>
       <c r="G36" t="s">
         <v>97</v>
@@ -2906,10 +2906,10 @@
         <v>96</v>
       </c>
       <c r="E37" t="s">
+        <v>96</v>
+      </c>
+      <c r="F37" t="s">
         <v>97</v>
-      </c>
-      <c r="F37" t="s">
-        <v>96</v>
       </c>
       <c r="G37" t="s">
         <v>97</v>
@@ -2929,10 +2929,10 @@
         <v>96</v>
       </c>
       <c r="E38" t="s">
+        <v>96</v>
+      </c>
+      <c r="F38" t="s">
         <v>97</v>
-      </c>
-      <c r="F38" t="s">
-        <v>96</v>
       </c>
       <c r="G38" t="s">
         <v>97</v>
@@ -2952,10 +2952,10 @@
         <v>96</v>
       </c>
       <c r="E39" t="s">
+        <v>96</v>
+      </c>
+      <c r="F39" t="s">
         <v>97</v>
-      </c>
-      <c r="F39" t="s">
-        <v>96</v>
       </c>
       <c r="G39" t="s">
         <v>97</v>
@@ -2975,10 +2975,10 @@
         <v>96</v>
       </c>
       <c r="E40" t="s">
+        <v>96</v>
+      </c>
+      <c r="F40" t="s">
         <v>97</v>
-      </c>
-      <c r="F40" t="s">
-        <v>96</v>
       </c>
       <c r="G40" t="s">
         <v>97</v>
@@ -2998,10 +2998,10 @@
         <v>108</v>
       </c>
       <c r="E41" t="s">
+        <v>108</v>
+      </c>
+      <c r="F41" t="s">
         <v>109</v>
-      </c>
-      <c r="F41" t="s">
-        <v>108</v>
       </c>
       <c r="G41" t="s">
         <v>109</v>
@@ -3021,10 +3021,10 @@
         <v>108</v>
       </c>
       <c r="E42" t="s">
+        <v>108</v>
+      </c>
+      <c r="F42" t="s">
         <v>109</v>
-      </c>
-      <c r="F42" t="s">
-        <v>108</v>
       </c>
       <c r="G42" t="s">
         <v>109</v>
@@ -3044,10 +3044,10 @@
         <v>108</v>
       </c>
       <c r="E43" t="s">
+        <v>108</v>
+      </c>
+      <c r="F43" t="s">
         <v>109</v>
-      </c>
-      <c r="F43" t="s">
-        <v>108</v>
       </c>
       <c r="G43" t="s">
         <v>109</v>
@@ -3067,10 +3067,10 @@
         <v>108</v>
       </c>
       <c r="E44" t="s">
+        <v>108</v>
+      </c>
+      <c r="F44" t="s">
         <v>109</v>
-      </c>
-      <c r="F44" t="s">
-        <v>108</v>
       </c>
       <c r="G44" t="s">
         <v>109</v>
@@ -3090,10 +3090,10 @@
         <v>108</v>
       </c>
       <c r="E45" t="s">
+        <v>108</v>
+      </c>
+      <c r="F45" t="s">
         <v>109</v>
-      </c>
-      <c r="F45" t="s">
-        <v>108</v>
       </c>
       <c r="G45" t="s">
         <v>109</v>
@@ -3113,10 +3113,10 @@
         <v>108</v>
       </c>
       <c r="E46" t="s">
+        <v>108</v>
+      </c>
+      <c r="F46" t="s">
         <v>109</v>
-      </c>
-      <c r="F46" t="s">
-        <v>108</v>
       </c>
       <c r="G46" t="s">
         <v>109</v>
@@ -3136,10 +3136,10 @@
         <v>108</v>
       </c>
       <c r="E47" t="s">
+        <v>108</v>
+      </c>
+      <c r="F47" t="s">
         <v>109</v>
-      </c>
-      <c r="F47" t="s">
-        <v>108</v>
       </c>
       <c r="G47" t="s">
         <v>109</v>
@@ -3159,10 +3159,10 @@
         <v>108</v>
       </c>
       <c r="E48" t="s">
+        <v>108</v>
+      </c>
+      <c r="F48" t="s">
         <v>109</v>
-      </c>
-      <c r="F48" t="s">
-        <v>108</v>
       </c>
       <c r="G48" t="s">
         <v>109</v>
@@ -3182,10 +3182,10 @@
         <v>108</v>
       </c>
       <c r="E49" t="s">
+        <v>108</v>
+      </c>
+      <c r="F49" t="s">
         <v>109</v>
-      </c>
-      <c r="F49" t="s">
-        <v>108</v>
       </c>
       <c r="G49" t="s">
         <v>109</v>
@@ -3205,10 +3205,10 @@
         <v>108</v>
       </c>
       <c r="E50" t="s">
+        <v>108</v>
+      </c>
+      <c r="F50" t="s">
         <v>109</v>
-      </c>
-      <c r="F50" t="s">
-        <v>108</v>
       </c>
       <c r="G50" t="s">
         <v>109</v>
@@ -3228,10 +3228,10 @@
         <v>108</v>
       </c>
       <c r="E51" t="s">
+        <v>108</v>
+      </c>
+      <c r="F51" t="s">
         <v>109</v>
-      </c>
-      <c r="F51" t="s">
-        <v>108</v>
       </c>
       <c r="G51" t="s">
         <v>109</v>
@@ -3622,10 +3622,10 @@
         <v>133</v>
       </c>
       <c r="F68" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="G68" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3645,10 +3645,10 @@
         <v>133</v>
       </c>
       <c r="F69" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="G69" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3668,10 +3668,10 @@
         <v>133</v>
       </c>
       <c r="F70" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="G70" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3691,10 +3691,10 @@
         <v>133</v>
       </c>
       <c r="F71" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="G71" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3714,10 +3714,10 @@
         <v>133</v>
       </c>
       <c r="F72" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="G72" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3737,10 +3737,10 @@
         <v>133</v>
       </c>
       <c r="F73" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="G73" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3757,10 +3757,10 @@
         <v>182</v>
       </c>
       <c r="E74" t="s">
+        <v>182</v>
+      </c>
+      <c r="F74" t="s">
         <v>183</v>
-      </c>
-      <c r="F74" t="s">
-        <v>182</v>
       </c>
       <c r="G74" t="s">
         <v>183</v>
@@ -3780,10 +3780,10 @@
         <v>182</v>
       </c>
       <c r="E75" t="s">
+        <v>182</v>
+      </c>
+      <c r="F75" t="s">
         <v>183</v>
-      </c>
-      <c r="F75" t="s">
-        <v>182</v>
       </c>
       <c r="G75" t="s">
         <v>183</v>
@@ -3803,10 +3803,10 @@
         <v>182</v>
       </c>
       <c r="E76" t="s">
+        <v>182</v>
+      </c>
+      <c r="F76" t="s">
         <v>183</v>
-      </c>
-      <c r="F76" t="s">
-        <v>182</v>
       </c>
       <c r="G76" t="s">
         <v>183</v>
@@ -3826,10 +3826,10 @@
         <v>182</v>
       </c>
       <c r="E77" t="s">
+        <v>182</v>
+      </c>
+      <c r="F77" t="s">
         <v>183</v>
-      </c>
-      <c r="F77" t="s">
-        <v>182</v>
       </c>
       <c r="G77" t="s">
         <v>183</v>
@@ -3849,10 +3849,10 @@
         <v>182</v>
       </c>
       <c r="E78" t="s">
+        <v>182</v>
+      </c>
+      <c r="F78" t="s">
         <v>183</v>
-      </c>
-      <c r="F78" t="s">
-        <v>182</v>
       </c>
       <c r="G78" t="s">
         <v>183</v>
@@ -3872,10 +3872,10 @@
         <v>182</v>
       </c>
       <c r="E79" t="s">
+        <v>182</v>
+      </c>
+      <c r="F79" t="s">
         <v>183</v>
-      </c>
-      <c r="F79" t="s">
-        <v>182</v>
       </c>
       <c r="G79" t="s">
         <v>183</v>
@@ -3895,10 +3895,10 @@
         <v>182</v>
       </c>
       <c r="E80" t="s">
+        <v>182</v>
+      </c>
+      <c r="F80" t="s">
         <v>183</v>
-      </c>
-      <c r="F80" t="s">
-        <v>182</v>
       </c>
       <c r="G80" t="s">
         <v>183</v>
@@ -3918,10 +3918,10 @@
         <v>182</v>
       </c>
       <c r="E81" t="s">
+        <v>182</v>
+      </c>
+      <c r="F81" t="s">
         <v>183</v>
-      </c>
-      <c r="F81" t="s">
-        <v>182</v>
       </c>
       <c r="G81" t="s">
         <v>183</v>
@@ -3941,10 +3941,10 @@
         <v>182</v>
       </c>
       <c r="E82" t="s">
+        <v>182</v>
+      </c>
+      <c r="F82" t="s">
         <v>183</v>
-      </c>
-      <c r="F82" t="s">
-        <v>182</v>
       </c>
       <c r="G82" t="s">
         <v>183</v>
@@ -3964,10 +3964,10 @@
         <v>182</v>
       </c>
       <c r="E83" t="s">
+        <v>182</v>
+      </c>
+      <c r="F83" t="s">
         <v>183</v>
-      </c>
-      <c r="F83" t="s">
-        <v>182</v>
       </c>
       <c r="G83" t="s">
         <v>183</v>
@@ -3987,10 +3987,10 @@
         <v>182</v>
       </c>
       <c r="E84" t="s">
+        <v>182</v>
+      </c>
+      <c r="F84" t="s">
         <v>183</v>
-      </c>
-      <c r="F84" t="s">
-        <v>182</v>
       </c>
       <c r="G84" t="s">
         <v>183</v>
@@ -4010,10 +4010,10 @@
         <v>206</v>
       </c>
       <c r="E85" t="s">
+        <v>206</v>
+      </c>
+      <c r="F85" t="s">
         <v>207</v>
-      </c>
-      <c r="F85" t="s">
-        <v>206</v>
       </c>
       <c r="G85" t="s">
         <v>207</v>
@@ -4033,10 +4033,10 @@
         <v>206</v>
       </c>
       <c r="E86" t="s">
+        <v>206</v>
+      </c>
+      <c r="F86" t="s">
         <v>207</v>
-      </c>
-      <c r="F86" t="s">
-        <v>206</v>
       </c>
       <c r="G86" t="s">
         <v>207</v>
@@ -4056,10 +4056,10 @@
         <v>206</v>
       </c>
       <c r="E87" t="s">
+        <v>206</v>
+      </c>
+      <c r="F87" t="s">
         <v>207</v>
-      </c>
-      <c r="F87" t="s">
-        <v>206</v>
       </c>
       <c r="G87" t="s">
         <v>207</v>
@@ -4079,10 +4079,10 @@
         <v>206</v>
       </c>
       <c r="E88" t="s">
+        <v>206</v>
+      </c>
+      <c r="F88" t="s">
         <v>207</v>
-      </c>
-      <c r="F88" t="s">
-        <v>206</v>
       </c>
       <c r="G88" t="s">
         <v>207</v>
@@ -4102,10 +4102,10 @@
         <v>206</v>
       </c>
       <c r="E89" t="s">
+        <v>206</v>
+      </c>
+      <c r="F89" t="s">
         <v>207</v>
-      </c>
-      <c r="F89" t="s">
-        <v>206</v>
       </c>
       <c r="G89" t="s">
         <v>207</v>
@@ -4125,10 +4125,10 @@
         <v>206</v>
       </c>
       <c r="E90" t="s">
+        <v>206</v>
+      </c>
+      <c r="F90" t="s">
         <v>207</v>
-      </c>
-      <c r="F90" t="s">
-        <v>206</v>
       </c>
       <c r="G90" t="s">
         <v>207</v>
@@ -4148,10 +4148,10 @@
         <v>206</v>
       </c>
       <c r="E91" t="s">
+        <v>206</v>
+      </c>
+      <c r="F91" t="s">
         <v>207</v>
-      </c>
-      <c r="F91" t="s">
-        <v>206</v>
       </c>
       <c r="G91" t="s">
         <v>207</v>
@@ -4171,10 +4171,10 @@
         <v>222</v>
       </c>
       <c r="E92" t="s">
+        <v>222</v>
+      </c>
+      <c r="F92" t="s">
         <v>223</v>
-      </c>
-      <c r="F92" t="s">
-        <v>222</v>
       </c>
       <c r="G92" t="s">
         <v>223</v>
@@ -4194,10 +4194,10 @@
         <v>222</v>
       </c>
       <c r="E93" t="s">
+        <v>222</v>
+      </c>
+      <c r="F93" t="s">
         <v>223</v>
-      </c>
-      <c r="F93" t="s">
-        <v>222</v>
       </c>
       <c r="G93" t="s">
         <v>223</v>
@@ -4217,10 +4217,10 @@
         <v>222</v>
       </c>
       <c r="E94" t="s">
+        <v>222</v>
+      </c>
+      <c r="F94" t="s">
         <v>223</v>
-      </c>
-      <c r="F94" t="s">
-        <v>222</v>
       </c>
       <c r="G94" t="s">
         <v>223</v>
@@ -4240,10 +4240,10 @@
         <v>222</v>
       </c>
       <c r="E95" t="s">
+        <v>222</v>
+      </c>
+      <c r="F95" t="s">
         <v>223</v>
-      </c>
-      <c r="F95" t="s">
-        <v>222</v>
       </c>
       <c r="G95" t="s">
         <v>223</v>
@@ -4358,10 +4358,10 @@
         <v>233</v>
       </c>
       <c r="F100" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="G100" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4381,10 +4381,10 @@
         <v>233</v>
       </c>
       <c r="F101" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="G101" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4404,10 +4404,10 @@
         <v>233</v>
       </c>
       <c r="F102" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="G102" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4427,10 +4427,10 @@
         <v>233</v>
       </c>
       <c r="F103" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="G103" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4450,10 +4450,10 @@
         <v>233</v>
       </c>
       <c r="F104" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="G104" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4473,10 +4473,10 @@
         <v>233</v>
       </c>
       <c r="F105" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="G105" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4496,10 +4496,10 @@
         <v>233</v>
       </c>
       <c r="F106" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="G106" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4519,10 +4519,10 @@
         <v>233</v>
       </c>
       <c r="F107" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="G107" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4542,10 +4542,10 @@
         <v>233</v>
       </c>
       <c r="F108" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="G108" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4565,10 +4565,10 @@
         <v>233</v>
       </c>
       <c r="F109" t="s">
-        <v>234</v>
+        <v>265</v>
       </c>
       <c r="G109" t="s">
-        <v>265</v>
+        <v>235</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4588,10 +4588,10 @@
         <v>233</v>
       </c>
       <c r="F110" t="s">
-        <v>234</v>
+        <v>265</v>
       </c>
       <c r="G110" t="s">
-        <v>265</v>
+        <v>235</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4611,10 +4611,10 @@
         <v>233</v>
       </c>
       <c r="F111" t="s">
-        <v>234</v>
+        <v>265</v>
       </c>
       <c r="G111" t="s">
-        <v>265</v>
+        <v>235</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4634,10 +4634,10 @@
         <v>233</v>
       </c>
       <c r="F112" t="s">
-        <v>234</v>
+        <v>265</v>
       </c>
       <c r="G112" t="s">
-        <v>265</v>
+        <v>235</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4657,10 +4657,10 @@
         <v>233</v>
       </c>
       <c r="F113" t="s">
-        <v>234</v>
+        <v>265</v>
       </c>
       <c r="G113" t="s">
-        <v>265</v>
+        <v>235</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4680,10 +4680,10 @@
         <v>233</v>
       </c>
       <c r="F114" t="s">
-        <v>234</v>
+        <v>265</v>
       </c>
       <c r="G114" t="s">
-        <v>265</v>
+        <v>235</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4703,10 +4703,10 @@
         <v>233</v>
       </c>
       <c r="F115" t="s">
-        <v>234</v>
+        <v>279</v>
       </c>
       <c r="G115" t="s">
-        <v>279</v>
+        <v>235</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4726,10 +4726,10 @@
         <v>233</v>
       </c>
       <c r="F116" t="s">
-        <v>234</v>
+        <v>283</v>
       </c>
       <c r="G116" t="s">
-        <v>283</v>
+        <v>235</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4749,10 +4749,10 @@
         <v>233</v>
       </c>
       <c r="F117" t="s">
-        <v>234</v>
+        <v>287</v>
       </c>
       <c r="G117" t="s">
-        <v>287</v>
+        <v>235</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4772,10 +4772,10 @@
         <v>233</v>
       </c>
       <c r="F118" t="s">
-        <v>234</v>
+        <v>287</v>
       </c>
       <c r="G118" t="s">
-        <v>287</v>
+        <v>235</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4795,10 +4795,10 @@
         <v>233</v>
       </c>
       <c r="F119" t="s">
-        <v>234</v>
+        <v>287</v>
       </c>
       <c r="G119" t="s">
-        <v>287</v>
+        <v>235</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4818,10 +4818,10 @@
         <v>233</v>
       </c>
       <c r="F120" t="s">
-        <v>234</v>
+        <v>287</v>
       </c>
       <c r="G120" t="s">
-        <v>287</v>
+        <v>235</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4841,10 +4841,10 @@
         <v>233</v>
       </c>
       <c r="F121" t="s">
-        <v>234</v>
+        <v>287</v>
       </c>
       <c r="G121" t="s">
-        <v>287</v>
+        <v>235</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4864,10 +4864,10 @@
         <v>233</v>
       </c>
       <c r="F122" t="s">
-        <v>234</v>
+        <v>287</v>
       </c>
       <c r="G122" t="s">
-        <v>287</v>
+        <v>235</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4887,10 +4887,10 @@
         <v>233</v>
       </c>
       <c r="F123" t="s">
-        <v>234</v>
+        <v>287</v>
       </c>
       <c r="G123" t="s">
-        <v>287</v>
+        <v>235</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4907,10 +4907,10 @@
         <v>302</v>
       </c>
       <c r="E124" t="s">
+        <v>302</v>
+      </c>
+      <c r="F124" t="s">
         <v>303</v>
-      </c>
-      <c r="F124" t="s">
-        <v>302</v>
       </c>
       <c r="G124" t="s">
         <v>303</v>
@@ -4930,10 +4930,10 @@
         <v>302</v>
       </c>
       <c r="E125" t="s">
+        <v>302</v>
+      </c>
+      <c r="F125" t="s">
         <v>303</v>
-      </c>
-      <c r="F125" t="s">
-        <v>302</v>
       </c>
       <c r="G125" t="s">
         <v>303</v>
@@ -4953,10 +4953,10 @@
         <v>302</v>
       </c>
       <c r="E126" t="s">
+        <v>302</v>
+      </c>
+      <c r="F126" t="s">
         <v>303</v>
-      </c>
-      <c r="F126" t="s">
-        <v>302</v>
       </c>
       <c r="G126" t="s">
         <v>303</v>
@@ -4976,10 +4976,10 @@
         <v>302</v>
       </c>
       <c r="E127" t="s">
+        <v>302</v>
+      </c>
+      <c r="F127" t="s">
         <v>303</v>
-      </c>
-      <c r="F127" t="s">
-        <v>302</v>
       </c>
       <c r="G127" t="s">
         <v>303</v>
@@ -4999,10 +4999,10 @@
         <v>302</v>
       </c>
       <c r="E128" t="s">
+        <v>302</v>
+      </c>
+      <c r="F128" t="s">
         <v>303</v>
-      </c>
-      <c r="F128" t="s">
-        <v>302</v>
       </c>
       <c r="G128" t="s">
         <v>303</v>
@@ -5022,10 +5022,10 @@
         <v>302</v>
       </c>
       <c r="E129" t="s">
+        <v>302</v>
+      </c>
+      <c r="F129" t="s">
         <v>303</v>
-      </c>
-      <c r="F129" t="s">
-        <v>302</v>
       </c>
       <c r="G129" t="s">
         <v>303</v>
@@ -5045,10 +5045,10 @@
         <v>316</v>
       </c>
       <c r="E130" t="s">
+        <v>316</v>
+      </c>
+      <c r="F130" t="s">
         <v>317</v>
-      </c>
-      <c r="F130" t="s">
-        <v>316</v>
       </c>
       <c r="G130" t="s">
         <v>317</v>
@@ -5068,10 +5068,10 @@
         <v>316</v>
       </c>
       <c r="E131" t="s">
+        <v>316</v>
+      </c>
+      <c r="F131" t="s">
         <v>317</v>
-      </c>
-      <c r="F131" t="s">
-        <v>316</v>
       </c>
       <c r="G131" t="s">
         <v>317</v>
@@ -5091,10 +5091,10 @@
         <v>316</v>
       </c>
       <c r="E132" t="s">
+        <v>316</v>
+      </c>
+      <c r="F132" t="s">
         <v>317</v>
-      </c>
-      <c r="F132" t="s">
-        <v>316</v>
       </c>
       <c r="G132" t="s">
         <v>317</v>
@@ -5114,10 +5114,10 @@
         <v>316</v>
       </c>
       <c r="E133" t="s">
+        <v>316</v>
+      </c>
+      <c r="F133" t="s">
         <v>317</v>
-      </c>
-      <c r="F133" t="s">
-        <v>316</v>
       </c>
       <c r="G133" t="s">
         <v>317</v>
@@ -5554,10 +5554,10 @@
         <v>327</v>
       </c>
       <c r="F152" t="s">
-        <v>328</v>
+        <v>367</v>
       </c>
       <c r="G152" t="s">
-        <v>367</v>
+        <v>329</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5577,10 +5577,10 @@
         <v>327</v>
       </c>
       <c r="F153" t="s">
-        <v>328</v>
+        <v>367</v>
       </c>
       <c r="G153" t="s">
-        <v>367</v>
+        <v>329</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5600,10 +5600,10 @@
         <v>327</v>
       </c>
       <c r="F154" t="s">
-        <v>328</v>
+        <v>367</v>
       </c>
       <c r="G154" t="s">
-        <v>367</v>
+        <v>329</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5623,10 +5623,10 @@
         <v>327</v>
       </c>
       <c r="F155" t="s">
-        <v>328</v>
+        <v>367</v>
       </c>
       <c r="G155" t="s">
-        <v>367</v>
+        <v>329</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5646,10 +5646,10 @@
         <v>327</v>
       </c>
       <c r="F156" t="s">
-        <v>328</v>
+        <v>367</v>
       </c>
       <c r="G156" t="s">
-        <v>367</v>
+        <v>329</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5669,10 +5669,10 @@
         <v>327</v>
       </c>
       <c r="F157" t="s">
-        <v>328</v>
+        <v>367</v>
       </c>
       <c r="G157" t="s">
-        <v>367</v>
+        <v>329</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5692,10 +5692,10 @@
         <v>327</v>
       </c>
       <c r="F158" t="s">
-        <v>328</v>
+        <v>381</v>
       </c>
       <c r="G158" t="s">
-        <v>381</v>
+        <v>329</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5715,10 +5715,10 @@
         <v>327</v>
       </c>
       <c r="F159" t="s">
-        <v>328</v>
+        <v>381</v>
       </c>
       <c r="G159" t="s">
-        <v>381</v>
+        <v>329</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5738,10 +5738,10 @@
         <v>327</v>
       </c>
       <c r="F160" t="s">
-        <v>328</v>
+        <v>381</v>
       </c>
       <c r="G160" t="s">
-        <v>381</v>
+        <v>329</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5761,10 +5761,10 @@
         <v>327</v>
       </c>
       <c r="F161" t="s">
-        <v>328</v>
+        <v>381</v>
       </c>
       <c r="G161" t="s">
-        <v>381</v>
+        <v>329</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5784,10 +5784,10 @@
         <v>327</v>
       </c>
       <c r="F162" t="s">
-        <v>328</v>
+        <v>381</v>
       </c>
       <c r="G162" t="s">
-        <v>381</v>
+        <v>329</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -6244,10 +6244,10 @@
         <v>393</v>
       </c>
       <c r="F182" t="s">
-        <v>394</v>
+        <v>435</v>
       </c>
       <c r="G182" t="s">
-        <v>435</v>
+        <v>395</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -6267,10 +6267,10 @@
         <v>393</v>
       </c>
       <c r="F183" t="s">
-        <v>394</v>
+        <v>435</v>
       </c>
       <c r="G183" t="s">
-        <v>435</v>
+        <v>395</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -6290,10 +6290,10 @@
         <v>393</v>
       </c>
       <c r="F184" t="s">
-        <v>394</v>
+        <v>435</v>
       </c>
       <c r="G184" t="s">
-        <v>435</v>
+        <v>395</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6313,10 +6313,10 @@
         <v>393</v>
       </c>
       <c r="F185" t="s">
-        <v>394</v>
+        <v>435</v>
       </c>
       <c r="G185" t="s">
-        <v>435</v>
+        <v>395</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -6336,10 +6336,10 @@
         <v>393</v>
       </c>
       <c r="F186" t="s">
-        <v>394</v>
+        <v>435</v>
       </c>
       <c r="G186" t="s">
-        <v>435</v>
+        <v>395</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -6359,10 +6359,10 @@
         <v>393</v>
       </c>
       <c r="F187" t="s">
-        <v>394</v>
+        <v>435</v>
       </c>
       <c r="G187" t="s">
-        <v>435</v>
+        <v>395</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -6382,10 +6382,10 @@
         <v>393</v>
       </c>
       <c r="F188" t="s">
-        <v>394</v>
+        <v>435</v>
       </c>
       <c r="G188" t="s">
-        <v>435</v>
+        <v>395</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -6405,10 +6405,10 @@
         <v>393</v>
       </c>
       <c r="F189" t="s">
-        <v>394</v>
+        <v>435</v>
       </c>
       <c r="G189" t="s">
-        <v>435</v>
+        <v>395</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -6428,10 +6428,10 @@
         <v>393</v>
       </c>
       <c r="F190" t="s">
-        <v>394</v>
+        <v>435</v>
       </c>
       <c r="G190" t="s">
-        <v>435</v>
+        <v>395</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6451,10 +6451,10 @@
         <v>393</v>
       </c>
       <c r="F191" t="s">
-        <v>394</v>
+        <v>435</v>
       </c>
       <c r="G191" t="s">
-        <v>435</v>
+        <v>395</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6474,10 +6474,10 @@
         <v>393</v>
       </c>
       <c r="F192" t="s">
-        <v>394</v>
+        <v>457</v>
       </c>
       <c r="G192" t="s">
-        <v>457</v>
+        <v>395</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6494,10 +6494,10 @@
         <v>460</v>
       </c>
       <c r="E193" t="s">
+        <v>460</v>
+      </c>
+      <c r="F193" t="s">
         <v>461</v>
-      </c>
-      <c r="F193" t="s">
-        <v>460</v>
       </c>
       <c r="G193" t="s">
         <v>461</v>
@@ -6517,10 +6517,10 @@
         <v>460</v>
       </c>
       <c r="E194" t="s">
+        <v>460</v>
+      </c>
+      <c r="F194" t="s">
         <v>461</v>
-      </c>
-      <c r="F194" t="s">
-        <v>460</v>
       </c>
       <c r="G194" t="s">
         <v>461</v>
@@ -6540,10 +6540,10 @@
         <v>460</v>
       </c>
       <c r="E195" t="s">
+        <v>460</v>
+      </c>
+      <c r="F195" t="s">
         <v>461</v>
-      </c>
-      <c r="F195" t="s">
-        <v>460</v>
       </c>
       <c r="G195" t="s">
         <v>461</v>
@@ -6563,10 +6563,10 @@
         <v>460</v>
       </c>
       <c r="E196" t="s">
+        <v>460</v>
+      </c>
+      <c r="F196" t="s">
         <v>461</v>
-      </c>
-      <c r="F196" t="s">
-        <v>460</v>
       </c>
       <c r="G196" t="s">
         <v>461</v>
@@ -6586,10 +6586,10 @@
         <v>460</v>
       </c>
       <c r="E197" t="s">
+        <v>460</v>
+      </c>
+      <c r="F197" t="s">
         <v>461</v>
-      </c>
-      <c r="F197" t="s">
-        <v>460</v>
       </c>
       <c r="G197" t="s">
         <v>461</v>
@@ -6609,10 +6609,10 @@
         <v>460</v>
       </c>
       <c r="E198" t="s">
+        <v>460</v>
+      </c>
+      <c r="F198" t="s">
         <v>461</v>
-      </c>
-      <c r="F198" t="s">
-        <v>460</v>
       </c>
       <c r="G198" t="s">
         <v>461</v>
@@ -6632,10 +6632,10 @@
         <v>474</v>
       </c>
       <c r="E199" t="s">
+        <v>474</v>
+      </c>
+      <c r="F199" t="s">
         <v>475</v>
-      </c>
-      <c r="F199" t="s">
-        <v>474</v>
       </c>
       <c r="G199" t="s">
         <v>475</v>
@@ -6655,10 +6655,10 @@
         <v>478</v>
       </c>
       <c r="E200" t="s">
+        <v>478</v>
+      </c>
+      <c r="F200" t="s">
         <v>479</v>
-      </c>
-      <c r="F200" t="s">
-        <v>478</v>
       </c>
       <c r="G200" t="s">
         <v>479</v>
@@ -6678,10 +6678,10 @@
         <v>478</v>
       </c>
       <c r="E201" t="s">
+        <v>478</v>
+      </c>
+      <c r="F201" t="s">
         <v>479</v>
-      </c>
-      <c r="F201" t="s">
-        <v>478</v>
       </c>
       <c r="G201" t="s">
         <v>479</v>
@@ -6701,10 +6701,10 @@
         <v>478</v>
       </c>
       <c r="E202" t="s">
+        <v>478</v>
+      </c>
+      <c r="F202" t="s">
         <v>479</v>
-      </c>
-      <c r="F202" t="s">
-        <v>478</v>
       </c>
       <c r="G202" t="s">
         <v>479</v>
@@ -6724,10 +6724,10 @@
         <v>478</v>
       </c>
       <c r="E203" t="s">
+        <v>478</v>
+      </c>
+      <c r="F203" t="s">
         <v>479</v>
-      </c>
-      <c r="F203" t="s">
-        <v>478</v>
       </c>
       <c r="G203" t="s">
         <v>479</v>
@@ -6747,10 +6747,10 @@
         <v>478</v>
       </c>
       <c r="E204" t="s">
+        <v>478</v>
+      </c>
+      <c r="F204" t="s">
         <v>479</v>
-      </c>
-      <c r="F204" t="s">
-        <v>478</v>
       </c>
       <c r="G204" t="s">
         <v>479</v>
@@ -6770,10 +6770,10 @@
         <v>478</v>
       </c>
       <c r="E205" t="s">
+        <v>478</v>
+      </c>
+      <c r="F205" t="s">
         <v>479</v>
-      </c>
-      <c r="F205" t="s">
-        <v>478</v>
       </c>
       <c r="G205" t="s">
         <v>479</v>
@@ -6793,10 +6793,10 @@
         <v>492</v>
       </c>
       <c r="E206" t="s">
+        <v>492</v>
+      </c>
+      <c r="F206" t="s">
         <v>493</v>
-      </c>
-      <c r="F206" t="s">
-        <v>492</v>
       </c>
       <c r="G206" t="s">
         <v>493</v>
@@ -6816,10 +6816,10 @@
         <v>492</v>
       </c>
       <c r="E207" t="s">
+        <v>492</v>
+      </c>
+      <c r="F207" t="s">
         <v>493</v>
-      </c>
-      <c r="F207" t="s">
-        <v>492</v>
       </c>
       <c r="G207" t="s">
         <v>493</v>
@@ -6839,10 +6839,10 @@
         <v>492</v>
       </c>
       <c r="E208" t="s">
+        <v>492</v>
+      </c>
+      <c r="F208" t="s">
         <v>493</v>
-      </c>
-      <c r="F208" t="s">
-        <v>492</v>
       </c>
       <c r="G208" t="s">
         <v>493</v>
@@ -6862,10 +6862,10 @@
         <v>492</v>
       </c>
       <c r="E209" t="s">
+        <v>492</v>
+      </c>
+      <c r="F209" t="s">
         <v>493</v>
-      </c>
-      <c r="F209" t="s">
-        <v>492</v>
       </c>
       <c r="G209" t="s">
         <v>493</v>
@@ -6885,10 +6885,10 @@
         <v>492</v>
       </c>
       <c r="E210" t="s">
+        <v>492</v>
+      </c>
+      <c r="F210" t="s">
         <v>493</v>
-      </c>
-      <c r="F210" t="s">
-        <v>492</v>
       </c>
       <c r="G210" t="s">
         <v>493</v>
@@ -6908,10 +6908,10 @@
         <v>492</v>
       </c>
       <c r="E211" t="s">
+        <v>492</v>
+      </c>
+      <c r="F211" t="s">
         <v>493</v>
-      </c>
-      <c r="F211" t="s">
-        <v>492</v>
       </c>
       <c r="G211" t="s">
         <v>493</v>
@@ -6931,10 +6931,10 @@
         <v>492</v>
       </c>
       <c r="E212" t="s">
+        <v>492</v>
+      </c>
+      <c r="F212" t="s">
         <v>493</v>
-      </c>
-      <c r="F212" t="s">
-        <v>492</v>
       </c>
       <c r="G212" t="s">
         <v>493</v>
@@ -6954,10 +6954,10 @@
         <v>492</v>
       </c>
       <c r="E213" t="s">
+        <v>492</v>
+      </c>
+      <c r="F213" t="s">
         <v>493</v>
-      </c>
-      <c r="F213" t="s">
-        <v>492</v>
       </c>
       <c r="G213" t="s">
         <v>493</v>
@@ -6977,10 +6977,10 @@
         <v>492</v>
       </c>
       <c r="E214" t="s">
+        <v>492</v>
+      </c>
+      <c r="F214" t="s">
         <v>493</v>
-      </c>
-      <c r="F214" t="s">
-        <v>492</v>
       </c>
       <c r="G214" t="s">
         <v>493</v>
@@ -7000,10 +7000,10 @@
         <v>492</v>
       </c>
       <c r="E215" t="s">
+        <v>492</v>
+      </c>
+      <c r="F215" t="s">
         <v>493</v>
-      </c>
-      <c r="F215" t="s">
-        <v>492</v>
       </c>
       <c r="G215" t="s">
         <v>493</v>
@@ -7023,10 +7023,10 @@
         <v>514</v>
       </c>
       <c r="E216" t="s">
+        <v>514</v>
+      </c>
+      <c r="F216" t="s">
         <v>515</v>
-      </c>
-      <c r="F216" t="s">
-        <v>514</v>
       </c>
       <c r="G216" t="s">
         <v>515</v>
@@ -7046,10 +7046,10 @@
         <v>518</v>
       </c>
       <c r="E217" t="s">
+        <v>518</v>
+      </c>
+      <c r="F217" t="s">
         <v>519</v>
-      </c>
-      <c r="F217" t="s">
-        <v>518</v>
       </c>
       <c r="G217" t="s">
         <v>519</v>
@@ -7069,10 +7069,10 @@
         <v>522</v>
       </c>
       <c r="E218" t="s">
+        <v>522</v>
+      </c>
+      <c r="F218" t="s">
         <v>523</v>
-      </c>
-      <c r="F218" t="s">
-        <v>522</v>
       </c>
       <c r="G218" t="s">
         <v>523</v>
@@ -7092,10 +7092,10 @@
         <v>522</v>
       </c>
       <c r="E219" t="s">
+        <v>522</v>
+      </c>
+      <c r="F219" t="s">
         <v>523</v>
-      </c>
-      <c r="F219" t="s">
-        <v>522</v>
       </c>
       <c r="G219" t="s">
         <v>523</v>
@@ -7115,10 +7115,10 @@
         <v>528</v>
       </c>
       <c r="E220" t="s">
+        <v>528</v>
+      </c>
+      <c r="F220" t="s">
         <v>529</v>
-      </c>
-      <c r="F220" t="s">
-        <v>528</v>
       </c>
       <c r="G220" t="s">
         <v>529</v>
@@ -7138,10 +7138,10 @@
         <v>528</v>
       </c>
       <c r="E221" t="s">
+        <v>528</v>
+      </c>
+      <c r="F221" t="s">
         <v>529</v>
-      </c>
-      <c r="F221" t="s">
-        <v>528</v>
       </c>
       <c r="G221" t="s">
         <v>529</v>
@@ -7161,10 +7161,10 @@
         <v>528</v>
       </c>
       <c r="E222" t="s">
+        <v>528</v>
+      </c>
+      <c r="F222" t="s">
         <v>529</v>
-      </c>
-      <c r="F222" t="s">
-        <v>528</v>
       </c>
       <c r="G222" t="s">
         <v>529</v>
@@ -7184,10 +7184,10 @@
         <v>528</v>
       </c>
       <c r="E223" t="s">
+        <v>528</v>
+      </c>
+      <c r="F223" t="s">
         <v>529</v>
-      </c>
-      <c r="F223" t="s">
-        <v>528</v>
       </c>
       <c r="G223" t="s">
         <v>529</v>
@@ -7207,10 +7207,10 @@
         <v>528</v>
       </c>
       <c r="E224" t="s">
+        <v>528</v>
+      </c>
+      <c r="F224" t="s">
         <v>529</v>
-      </c>
-      <c r="F224" t="s">
-        <v>528</v>
       </c>
       <c r="G224" t="s">
         <v>529</v>
@@ -7230,10 +7230,10 @@
         <v>528</v>
       </c>
       <c r="E225" t="s">
+        <v>528</v>
+      </c>
+      <c r="F225" t="s">
         <v>529</v>
-      </c>
-      <c r="F225" t="s">
-        <v>528</v>
       </c>
       <c r="G225" t="s">
         <v>529</v>
@@ -7253,10 +7253,10 @@
         <v>528</v>
       </c>
       <c r="E226" t="s">
+        <v>528</v>
+      </c>
+      <c r="F226" t="s">
         <v>529</v>
-      </c>
-      <c r="F226" t="s">
-        <v>528</v>
       </c>
       <c r="G226" t="s">
         <v>529</v>
@@ -7276,10 +7276,10 @@
         <v>544</v>
       </c>
       <c r="E227" t="s">
+        <v>544</v>
+      </c>
+      <c r="F227" t="s">
         <v>545</v>
-      </c>
-      <c r="F227" t="s">
-        <v>544</v>
       </c>
       <c r="G227" t="s">
         <v>545</v>
@@ -7299,10 +7299,10 @@
         <v>544</v>
       </c>
       <c r="E228" t="s">
+        <v>544</v>
+      </c>
+      <c r="F228" t="s">
         <v>545</v>
-      </c>
-      <c r="F228" t="s">
-        <v>544</v>
       </c>
       <c r="G228" t="s">
         <v>545</v>
@@ -7322,10 +7322,10 @@
         <v>544</v>
       </c>
       <c r="E229" t="s">
+        <v>544</v>
+      </c>
+      <c r="F229" t="s">
         <v>545</v>
-      </c>
-      <c r="F229" t="s">
-        <v>544</v>
       </c>
       <c r="G229" t="s">
         <v>545</v>
@@ -7345,10 +7345,10 @@
         <v>552</v>
       </c>
       <c r="E230" t="s">
+        <v>552</v>
+      </c>
+      <c r="F230" t="s">
         <v>553</v>
-      </c>
-      <c r="F230" t="s">
-        <v>552</v>
       </c>
       <c r="G230" t="s">
         <v>553</v>
@@ -7368,10 +7368,10 @@
         <v>556</v>
       </c>
       <c r="E231" t="s">
+        <v>556</v>
+      </c>
+      <c r="F231" t="s">
         <v>557</v>
-      </c>
-      <c r="F231" t="s">
-        <v>556</v>
       </c>
       <c r="G231" t="s">
         <v>557</v>
@@ -7391,10 +7391,10 @@
         <v>560</v>
       </c>
       <c r="E232" t="s">
+        <v>560</v>
+      </c>
+      <c r="F232" t="s">
         <v>561</v>
-      </c>
-      <c r="F232" t="s">
-        <v>560</v>
       </c>
       <c r="G232" t="s">
         <v>561</v>
@@ -7414,10 +7414,10 @@
         <v>564</v>
       </c>
       <c r="E233" t="s">
+        <v>564</v>
+      </c>
+      <c r="F233" t="s">
         <v>565</v>
-      </c>
-      <c r="F233" t="s">
-        <v>564</v>
       </c>
       <c r="G233" t="s">
         <v>565</v>
@@ -7437,10 +7437,10 @@
         <v>568</v>
       </c>
       <c r="E234" t="s">
+        <v>568</v>
+      </c>
+      <c r="F234" t="s">
         <v>569</v>
-      </c>
-      <c r="F234" t="s">
-        <v>568</v>
       </c>
       <c r="G234" t="s">
         <v>569</v>
@@ -7460,10 +7460,10 @@
         <v>568</v>
       </c>
       <c r="E235" t="s">
+        <v>568</v>
+      </c>
+      <c r="F235" t="s">
         <v>569</v>
-      </c>
-      <c r="F235" t="s">
-        <v>568</v>
       </c>
       <c r="G235" t="s">
         <v>569</v>
